--- a/online food delivery analysis..xlsx
+++ b/online food delivery analysis..xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\OneDrive\Desktop\Projects\Complete\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -817,7 +817,139 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="55">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="0.00000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="170" formatCode="0.0000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
@@ -828,28 +960,28 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="0.0"/>
+      <numFmt numFmtId="165" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="0.000"/>
+      <numFmt numFmtId="166" formatCode="0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.0000"/>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="168" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="0.000000"/>
+      <numFmt numFmtId="169" formatCode="0.000000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000000"/>
+      <numFmt numFmtId="170" formatCode="0.0000000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000000"/>
+      <numFmt numFmtId="171" formatCode="0.00000000"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -878,7 +1010,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Segment mix by Occupation!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Segment mix by Occupation!PivotTable1</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -2136,7 +2268,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Output by Age Group!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Output by Age Group!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -2555,8 +2687,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.037270341207349E-2"/>
-          <c:y val="0.19115929587562733"/>
+          <c:x val="9.7356439700680503E-2"/>
+          <c:y val="0.1911593426884298"/>
           <c:w val="0.8624793353363418"/>
           <c:h val="0.69982689332478021"/>
         </c:manualLayout>
@@ -3032,7 +3164,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Segment mix by Occupation!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Segment mix by Occupation!PivotTable1</c:name>
     <c:fmtId val="10"/>
   </c:pivotSource>
   <c:chart>
@@ -4480,7 +4612,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Feedback by Gender!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Feedback by Gender!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -5437,7 +5569,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Feedback by Customer Type!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Feedback by Customer Type!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -5843,8 +5975,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.14997807770393201"/>
-          <c:y val="8.8379629629629614E-2"/>
+          <c:x val="0.14997822901388957"/>
+          <c:y val="7.5471630994832298E-2"/>
           <c:w val="0.72963676780213638"/>
           <c:h val="0.80422098279381748"/>
         </c:manualLayout>
@@ -6273,7 +6405,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Feedback by Education!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Feedback by Education!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -6715,8 +6847,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.29383838509389909"/>
-          <c:y val="0.23405398153577073"/>
+          <c:x val="0.27319351836107819"/>
+          <c:y val="0.20153049987861305"/>
           <c:w val="0.65265676180108845"/>
           <c:h val="0.61955489083446791"/>
         </c:manualLayout>
@@ -7214,7 +7346,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Avg Family Size by Occupation!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Avg Family Size by Occupation!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -7769,7 +7901,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Overall Output split!PivotTable2</c:name>
+    <c:name>[online food delivery analysis..xlsx]Overall Output split!PivotTable2</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -8638,7 +8770,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Output by Income bracket!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Output by Income bracket!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -9316,7 +9448,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Output by Age Group!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Output by Age Group!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -9972,7 +10104,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Feedback by Gender!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Feedback by Gender!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -10610,7 +10742,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Feedback by Customer Type!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Feedback by Customer Type!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -11223,7 +11355,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Feedback by Education!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Feedback by Education!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -11916,7 +12048,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Avg Family Size by Occupation!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Avg Family Size by Occupation!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -12346,7 +12478,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Overall Output split!PivotTable2</c:name>
+    <c:name>[online food delivery analysis..xlsx]Overall Output split!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -12872,7 +13004,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[online food delivery dataset..xlsx]Output by Income bracket!PivotTable1</c:name>
+    <c:name>[online food delivery analysis..xlsx]Output by Income bracket!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -12907,8 +13039,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="4.0369386411631722E-2"/>
-          <c:y val="2.1467410072550142E-2"/>
+          <c:x val="4.0369308415340928E-2"/>
+          <c:y val="2.1467421422066639E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -13291,8 +13423,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.12190872238040372"/>
-          <c:y val="0.23405409783363204"/>
+          <c:x val="0.13461304410020503"/>
+          <c:y val="0.22756764017719014"/>
           <c:w val="0.8097991479001827"/>
           <c:h val="0.50802692519250559"/>
         </c:manualLayout>
@@ -22247,16 +22379,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>445526</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>52743</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>186574</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>7682</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>302269</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>92177</xdr:rowOff>
+      <xdr:rowOff>82358</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22279,16 +22411,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>2</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>7682</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>333868</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>154976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>330303</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>7682</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>664169</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>154975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22311,16 +22443,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>343687</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>186573</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>330302</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>673988</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>115221</xdr:rowOff>
+      <xdr:rowOff>105401</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22343,16 +22475,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>445525</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>7680</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>42921</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>174614</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>38407</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>323173</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>166933</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22375,16 +22507,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>324048</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>107540</xdr:rowOff>
+      <xdr:rowOff>68264</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>330302</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>23045</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>654350</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>170341</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22407,16 +22539,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>445525</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>42922</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>99860</xdr:rowOff>
+      <xdr:rowOff>70402</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>84497</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>369264</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>157114</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22439,16 +22571,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>130584</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>7682</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>405532</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>194255</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>414798</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>2376</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>99859</xdr:rowOff>
+      <xdr:rowOff>90040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22471,16 +22603,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>138266</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>7681</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>403394</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>184434</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>430161</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>7919</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>122903</xdr:rowOff>
+      <xdr:rowOff>113083</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22503,19 +22635,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>499601</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>83576</xdr:rowOff>
+      <xdr:rowOff>14839</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>53770</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>241540</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>117836</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="Age group"/>
@@ -22532,7 +22664,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22542,8 +22674,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9387041" y="283294"/>
-              <a:ext cx="921467" cy="1068642"/>
+              <a:off x="0" y="211231"/>
+              <a:ext cx="928911" cy="1035858"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22575,19 +22707,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>499601</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>37487</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>165141</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>61452</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>249222</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>84497</xdr:rowOff>
+      <xdr:rowOff>25579</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Gender"/>
@@ -22604,7 +22736,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22614,8 +22746,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9387041" y="1389422"/>
-              <a:ext cx="929149" cy="815156"/>
+              <a:off x="0" y="1294394"/>
+              <a:ext cx="936593" cy="793298"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22647,19 +22779,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>491921</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>121982</xdr:rowOff>
+      <xdr:rowOff>92523</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>76814</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>272264</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>61452</xdr:rowOff>
+      <xdr:rowOff>31993</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="Marital Status"/>
@@ -22676,7 +22808,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22686,8 +22818,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9379361" y="2242063"/>
-              <a:ext cx="952191" cy="1091687"/>
+              <a:off x="0" y="2154636"/>
+              <a:ext cx="959635" cy="1058903"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22719,19 +22851,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>107848</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>480993</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>60529</xdr:rowOff>
+      <xdr:rowOff>1612</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>545383</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>231157</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>115222</xdr:rowOff>
+      <xdr:rowOff>56305</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="13" name="Occupation"/>
@@ -22748,7 +22880,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22758,8 +22890,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10362586" y="260247"/>
-              <a:ext cx="1121184" cy="1398947"/>
+              <a:off x="1168364" y="198004"/>
+              <a:ext cx="1124906" cy="1360698"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22791,19 +22923,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>100166</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>473310</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>175753</xdr:rowOff>
+      <xdr:rowOff>126654</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>553065</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>238838</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>115223</xdr:rowOff>
+      <xdr:rowOff>66124</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="14" name="Monthly Income"/>
@@ -22820,7 +22952,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22830,8 +22962,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10354904" y="1719725"/>
-              <a:ext cx="1136548" cy="1667796"/>
+              <a:off x="1160681" y="1629051"/>
+              <a:ext cx="1140270" cy="1618619"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22863,19 +22995,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>123211</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>490980</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>160390</xdr:rowOff>
+      <xdr:rowOff>140750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>553065</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>233463</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>53770</xdr:rowOff>
+      <xdr:rowOff>34130</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="15" name="Educational Qualifications"/>
@@ -22892,7 +23024,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22902,8 +23034,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10377949" y="3432688"/>
-              <a:ext cx="1113503" cy="1621707"/>
+              <a:off x="1178351" y="3322296"/>
+              <a:ext cx="1117225" cy="1572530"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -22935,19 +23067,19 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>499601</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:rowOff>84843</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>69133</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>23044</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>256903</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>180158</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="16" name="Customer Type"/>
@@ -22964,7 +23096,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -22974,8 +23106,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9387041" y="3386599"/>
-              <a:ext cx="936830" cy="1060961"/>
+              <a:off x="0" y="3266389"/>
+              <a:ext cx="944274" cy="1028176"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -31192,63 +31324,63 @@
     <dataField name="Average of Family size" fld="7" subtotal="average" baseField="4" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="10">
+    <format dxfId="54">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="53">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="52">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="51">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="50">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="49">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="48">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="47">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="46">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
@@ -31382,14 +31514,14 @@
     <dataField name="Percentage" fld="12" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="45">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="44">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="0"/>
